--- a/healthcare_forms/050_tell_us_about_yourself--healthcare_forms.xlsx
+++ b/healthcare_forms/050_tell_us_about_yourself--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>non_hispanic</t>
+          <t>non hispanic</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>less_than_high_school</t>
+          <t>less than high school</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>some_college</t>
+          <t>some college</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>less_than_10000</t>
+          <t>less than 10000</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10000_to_20000</t>
+          <t>10000 to 20000</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20000_to_50000</t>
+          <t>20000 to 50000</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>50000_to_75000</t>
+          <t>50000 to 75000</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>75000_to_100000</t>
+          <t>75000 to 100000</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100000_to_150000</t>
+          <t>100000 to 150000</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>more_than_150000</t>
+          <t>more than 150000</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>not working</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>less_than_1_year</t>
+          <t>less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1_to_2_years</t>
+          <t>1 to 2 years</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2_to_5_years</t>
+          <t>2 to 5 years</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>more_than_5_years</t>
+          <t>more than 5 years</t>
         </is>
       </c>
     </row>
